--- a/src/data/COREP_files/G_EU_C_C2400.xlsx
+++ b/src/data/COREP_files/G_EU_C_C2400.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1"/>
@@ -621,10 +621,40 @@
           <t xml:space="preserve"> TOTAL POSITIONS</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>13</v>
+      </c>
+      <c r="I7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>Cell linked to CA</t>
         </is>
+      </c>
+      <c r="P7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>13</v>
+      </c>
+      <c r="R7" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -669,6 +699,39 @@
           <t>TDI - Specific Risk</t>
         </is>
       </c>
+      <c r="E11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" t="n">
+        <v>14</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" t="n">
+        <v>16</v>
+      </c>
+      <c r="I11" t="n">
+        <v>17</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18</v>
+      </c>
+      <c r="N11" t="n">
+        <v>13</v>
+      </c>
+      <c r="O11" t="n">
+        <v>14</v>
+      </c>
+      <c r="P11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>16</v>
+      </c>
+      <c r="R11" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -754,7 +817,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
